--- a/data/trans_orig/P6906-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6906-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>32230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>25278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39115</t>
+          <t>39233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55662</t>
+          <t>56111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46834</t>
+          <t>45563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63050</t>
+          <t>62648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29928</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71538</t>
+          <t>71331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90590</t>
+          <t>91031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>34605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53601</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52182</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59485</t>
+          <t>58757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73462</t>
+          <t>73149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>28968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49941</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25080</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63368</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36825</t>
+          <t>36911</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94363</t>
+          <t>94405</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114180</t>
+          <t>113673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>38872</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55816</t>
+          <t>55408</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>70043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87843</t>
+          <t>87365</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28056</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>41355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102885</t>
+          <t>103293</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>125096</t>
+          <t>126238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,54%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88075</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126925</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>62153</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>133854</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>177728</t>
+          <t>178065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>345380</t>
+          <t>345968</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>384230</t>
+          <t>382619</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>159608</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>183422</t>
+          <t>183952</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>514699</t>
+          <t>514362</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>558573</t>
+          <t>560019</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>25342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>40133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33073</t>
+          <t>33520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>32033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45870</t>
+          <t>45945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31446</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57832</t>
+          <t>57385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74138</t>
+          <t>75065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>36437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41536</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56918</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26847</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30721</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>40499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40033</t>
+          <t>39607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36137</t>
+          <t>35939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>32982</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47146</t>
+          <t>46605</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>26466</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38479</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>64871</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>82885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32150</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42857</t>
+          <t>42896</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52268</t>
+          <t>51987</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67120</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>68102</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>100999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50884</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77900</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127966</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>169978</t>
+          <t>172629</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>224796</t>
+          <t>225226</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>258123</t>
+          <t>257043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136935</t>
+          <t>136457</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163951</t>
+          <t>164149</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>371082</t>
+          <t>368431</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>413094</t>
+          <t>412365</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25520</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29998</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>51606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>29602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44632</t>
+          <t>44997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48422</t>
+          <t>47855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69463</t>
+          <t>68192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23109</t>
+          <t>21188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59677</t>
+          <t>61598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75294</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24896</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35885</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90552</t>
+          <t>90424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108987</t>
+          <t>109365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42895</t>
+          <t>41488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>17606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39117</t>
+          <t>39733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54695</t>
+          <t>55067</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>70131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34952</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47718</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94907</t>
+          <t>94291</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114281</t>
+          <t>114673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>33202</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51130</t>
+          <t>50874</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67365</t>
+          <t>66641</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>100637</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>134773</t>
+          <t>132743</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>177346</t>
+          <t>177122</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>248080</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>282636</t>
+          <t>283360</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130601</t>
+          <t>132807</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>160478</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>388953</t>
+          <t>389177</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>431526</t>
+          <t>433556</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40008</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40181</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>51909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71386</t>
+          <t>71002</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35256</t>
+          <t>36337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>46088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29497</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>38781</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69812</t>
+          <t>69690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83297</t>
+          <t>83294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45622</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>48957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75246</t>
+          <t>75908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75383</t>
+          <t>76157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108961</t>
+          <t>108410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27610</t>
+          <t>27526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21669</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29691</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42500</t>
+          <t>43057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>53820</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>29946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28061</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>49991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>65539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>40581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53477</t>
+          <t>54134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96394</t>
+          <t>96233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>115644</t>
+          <t>115988</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>45601</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54684</t>
+          <t>54797</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41329</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51033</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>90653</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>104165</t>
+          <t>104311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50125</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>82915</t>
+          <t>82439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106237</t>
+          <t>106128</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127376</t>
+          <t>128239</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>181106</t>
+          <t>177729</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>256590</t>
+          <t>257066</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>289380</t>
+          <t>290226</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>247978</t>
+          <t>248087</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>289821</t>
+          <t>290422</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>512614</t>
+          <t>515991</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>566344</t>
+          <t>565481</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
